--- a/results/04_bray_curtis_NMDS/tables/nmds_summary.xlsx
+++ b/results/04_bray_curtis_NMDS/tables/nmds_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,16 +470,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>155</v>
+        <v>204</v>
       </c>
       <c r="C2" t="n">
-        <v>0.151571837605715</v>
+        <v>0.1591477908475909</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5929220039822287</v>
+        <v>0.6301154739271609</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4070779960177712</v>
+        <v>0.369884526072839</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -509,29 +509,6 @@
       </c>
       <c r="G3" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>49</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.1138550656144115</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.729702942255167</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.270297057744833</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_bray_curtis_NMDS/tables/nmds_summary.xlsx
+++ b/results/04_bray_curtis_NMDS/tables/nmds_summary.xlsx
@@ -470,16 +470,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1591477908475909</v>
+        <v>0.1966602350105597</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6301154739271609</v>
+        <v>0.5563660466984272</v>
       </c>
       <c r="E2" t="n">
-        <v>0.369884526072839</v>
+        <v>0.4436339533015728</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -493,22 +493,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>0.114297527659565</v>
+        <v>0.08522454564191566</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5807069800929726</v>
+        <v>0.7809416696381769</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4192930199070274</v>
+        <v>0.2190583303618231</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
       </c>
       <c r="G3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
